--- a/tasks/medical_careig_specialty_pharmacy_3c62ee67/environment/initial_workspace/DENIAL_PI204_12092025.xlsx
+++ b/tasks/medical_careig_specialty_pharmacy_3c62ee67/environment/initial_workspace/DENIAL_PI204_12092025.xlsx
@@ -3,6 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15"/>
+  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD17128-D606-4079-A9D3-9478D27051D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
